--- a/Design Files/Ezlo-Thermostat-v2.0-Advance/BOM/Client_BOM.xlsx
+++ b/Design Files/Ezlo-Thermostat-v2.0-Advance/BOM/Client_BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="271">
   <si>
     <t>#</t>
   </si>
@@ -825,13 +825,13 @@
     <t>Camera</t>
   </si>
   <si>
-    <t xml:space="preserve">Cable </t>
-  </si>
-  <si>
-    <t>tablet connect to PCB</t>
-  </si>
-  <si>
-    <t>Length Required</t>
+    <t xml:space="preserve">A10SR10SR30K102A </t>
+  </si>
+  <si>
+    <t>JUMPER 10SR-3S - 10SR-3S 4"</t>
+  </si>
+  <si>
+    <t>JST Sales America Inc.</t>
   </si>
 </sst>
 </file>
@@ -1175,9 +1175,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1198,6 +1195,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1510,9 +1510,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1553,7 +1553,7 @@
         <f>ROW(B3) - ROW($B$2)</f>
         <v>1</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="15" t="s">
@@ -1585,7 +1585,7 @@
         <f t="shared" ref="B4:B54" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="17" t="s">
@@ -1617,7 +1617,7 @@
         <f>ROW(B5) - ROW($B$2)</f>
         <v>3</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="15" t="s">
@@ -1649,7 +1649,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="24" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="17" t="s">
@@ -1681,7 +1681,7 @@
         <f>ROW(B7) - ROW($B$2)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="24" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="15" t="s">
@@ -1713,7 +1713,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="24" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="17" t="s">
@@ -1745,7 +1745,7 @@
         <f>ROW(B9) - ROW($B$2)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="24" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="15" t="s">
@@ -1777,7 +1777,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="17" t="s">
@@ -1809,7 +1809,7 @@
         <f>ROW(B11) - ROW($B$2)</f>
         <v>9</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="24" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="15" t="s">
@@ -1841,7 +1841,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="24" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="17" t="s">
@@ -1873,7 +1873,7 @@
         <f>ROW(B13) - ROW($B$2)</f>
         <v>11</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="24" t="s">
         <v>260</v>
       </c>
       <c r="D13" s="15" t="s">
@@ -1905,7 +1905,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="17" t="s">
@@ -1937,7 +1937,7 @@
         <f>ROW(B15) - ROW($B$2)</f>
         <v>13</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="15" t="s">
@@ -1969,7 +1969,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="25" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="17" t="s">
@@ -2001,7 +2001,7 @@
         <f>ROW(B17) - ROW($B$2)</f>
         <v>15</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="24" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="15" t="s">
@@ -2033,7 +2033,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="25" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="17" t="s">
@@ -2065,7 +2065,7 @@
         <f>ROW(B19) - ROW($B$2)</f>
         <v>17</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="24" t="s">
         <v>261</v>
       </c>
       <c r="D19" s="15" t="s">
@@ -2097,7 +2097,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="25" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="17" t="s">
@@ -2129,7 +2129,7 @@
         <f>ROW(B21) - ROW($B$2)</f>
         <v>19</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="24" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="15" t="s">
@@ -2161,7 +2161,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="17" t="s">
@@ -2193,7 +2193,7 @@
         <f>ROW(B23) - ROW($B$2)</f>
         <v>21</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="15" t="s">
@@ -2225,7 +2225,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="25" t="s">
         <v>262</v>
       </c>
       <c r="D24" s="17" t="s">
@@ -2255,7 +2255,7 @@
         <f>ROW(B25) - ROW($B$2)</f>
         <v>23</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="24" t="s">
         <v>262</v>
       </c>
       <c r="D25" s="15" t="s">
@@ -2285,7 +2285,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="25" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="17" t="s">
@@ -2317,7 +2317,7 @@
         <f>ROW(B27) - ROW($B$2)</f>
         <v>25</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="24" t="s">
         <v>11</v>
       </c>
       <c r="D27" s="15" t="s">
@@ -2349,7 +2349,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="25" t="s">
         <v>12</v>
       </c>
       <c r="D28" s="17" t="s">
@@ -2381,7 +2381,7 @@
         <f>ROW(B29) - ROW($B$2)</f>
         <v>27</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="24" t="s">
         <v>12</v>
       </c>
       <c r="D29" s="15" t="s">
@@ -2413,7 +2413,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="25" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="17" t="s">
@@ -2445,26 +2445,26 @@
         <f>ROW(B31) - ROW($B$2)</f>
         <v>29</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="29" t="s">
+      <c r="E31" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="27" t="s">
         <v>264</v>
       </c>
-      <c r="G31" s="28" t="s">
+      <c r="G31" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="H31" s="28"/>
-      <c r="I31" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="J31" s="28">
+      <c r="H31" s="27"/>
+      <c r="I31" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="J31" s="27">
         <v>25</v>
       </c>
       <c r="K31" s="15"/>
@@ -2475,7 +2475,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="17" t="s">
@@ -2507,7 +2507,7 @@
         <f>ROW(B33) - ROW($B$2)</f>
         <v>31</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="24" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="15" t="s">
@@ -2539,7 +2539,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="17" t="s">
@@ -2571,7 +2571,7 @@
         <f>ROW(B35) - ROW($B$2)</f>
         <v>33</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="15" t="s">
@@ -2603,7 +2603,7 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D36" s="17" t="s">
@@ -2635,7 +2635,7 @@
         <f>ROW(B37) - ROW($B$2)</f>
         <v>35</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="15" t="s">
@@ -2667,7 +2667,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="17" t="s">
@@ -2699,7 +2699,7 @@
         <f>ROW(B39) - ROW($B$2)</f>
         <v>37</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D39" s="15" t="s">
@@ -2731,7 +2731,7 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C40" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D40" s="17" t="s">
@@ -2763,7 +2763,7 @@
         <f>ROW(B41) - ROW($B$2)</f>
         <v>39</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="24" t="s">
         <v>15</v>
       </c>
       <c r="D41" s="15" t="s">
@@ -2795,7 +2795,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="17" t="s">
@@ -2827,7 +2827,7 @@
         <f>ROW(B43) - ROW($B$2)</f>
         <v>41</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="C43" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D43" s="15" t="s">
@@ -2859,7 +2859,7 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C44" s="25" t="s">
         <v>16</v>
       </c>
       <c r="D44" s="17" t="s">
@@ -2891,7 +2891,7 @@
         <f>ROW(B45) - ROW($B$2)</f>
         <v>43</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="24" t="s">
         <v>17</v>
       </c>
       <c r="D45" s="15" t="s">
@@ -2923,7 +2923,7 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C46" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D46" s="17" t="s">
@@ -2955,7 +2955,7 @@
         <f>ROW(B47) - ROW($B$2)</f>
         <v>45</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="24" t="s">
         <v>18</v>
       </c>
       <c r="D47" s="15" t="s">
@@ -2987,7 +2987,7 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C48" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D48" s="17" t="s">
@@ -3019,7 +3019,7 @@
         <f>ROW(B49) - ROW($B$2)</f>
         <v>47</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="24" t="s">
         <v>19</v>
       </c>
       <c r="D49" s="15" t="s">
@@ -3051,7 +3051,7 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C50" s="26" t="s">
+      <c r="C50" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D50" s="17" t="s">
@@ -3083,7 +3083,7 @@
         <f>ROW(B51) - ROW($B$2)</f>
         <v>49</v>
       </c>
-      <c r="C51" s="25" t="s">
+      <c r="C51" s="24" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="15" t="s">
@@ -3115,7 +3115,7 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C52" s="26" t="s">
+      <c r="C52" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D52" s="17" t="s">
@@ -3147,7 +3147,7 @@
         <f>ROW(B53) - ROW($B$2)</f>
         <v>51</v>
       </c>
-      <c r="C53" s="25" t="s">
+      <c r="C53" s="24" t="s">
         <v>20</v>
       </c>
       <c r="D53" s="15" t="s">
@@ -3179,7 +3179,7 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C54" s="26" t="s">
+      <c r="C54" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D54" s="17" t="s">
@@ -3211,7 +3211,7 @@
         <f>ROW(B55) - ROW($B$2)</f>
         <v>53</v>
       </c>
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="24" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="15" t="s">
@@ -3243,10 +3243,12 @@
         <f t="shared" ref="B56:B58" si="1">ROW(B56) - ROW($B$2)</f>
         <v>54</v>
       </c>
-      <c r="C56" s="25" t="s">
+      <c r="C56" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="D56" s="15"/>
+      <c r="D56" s="15" t="s">
+        <v>259</v>
+      </c>
       <c r="E56" s="16"/>
       <c r="F56" s="15"/>
       <c r="G56" s="16" t="s">
@@ -3265,10 +3267,12 @@
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="D57" s="15"/>
+      <c r="D57" s="15" t="s">
+        <v>259</v>
+      </c>
       <c r="E57" s="16"/>
       <c r="F57" s="15"/>
       <c r="G57" s="16" t="s">
@@ -3287,10 +3291,12 @@
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="D58" s="15"/>
+      <c r="D58" s="15" t="s">
+        <v>259</v>
+      </c>
       <c r="E58" s="16" t="s">
         <v>269</v>
       </c>
@@ -3300,12 +3306,16 @@
       <c r="G58" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="H58" s="15"/>
-      <c r="I58" s="16"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="31" t="s">
+      <c r="H58" s="15" t="s">
         <v>270</v>
       </c>
+      <c r="I58" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="J58" s="15">
+        <v>1</v>
+      </c>
+      <c r="K58" s="30"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
